--- a/templates/farmacia_excel_operativo_FH_WO8_v1_sintetico.xlsx
+++ b/templates/farmacia_excel_operativo_FH_WO8_v1_sintetico.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_DERMA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_REUMA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_DIGESTIVO" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_ONCO" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_CATALOGOS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_CONFIG_EXPORT_MAP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="01_DERMA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_REUMA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_DIGESTIVO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_ONCO" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_CATALOGOS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="99_CONFIG_EXPORT_MAP" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_DERMA'!$A$1:$BI$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02_REUMA'!$A$1:$BI$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03_DIGESTIVO'!$A$1:$BI$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04_ONCO'!$A$1:$BI$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_DERMA'!$A$1:$BJ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02_REUMA'!$A$1:$BJ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03_DIGESTIVO'!$A$1:$BJ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04_ONCO'!$A$1:$BJ$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI11"/>
+  <dimension ref="A1:BJ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -614,6 +614,7 @@
     <col width="18" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="28" customWidth="1" min="61" max="61"/>
+    <col width="20" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -920,6 +921,11 @@
       <c r="BI1" s="7" t="inlineStr">
         <is>
           <t>observaciones_generales</t>
+        </is>
+      </c>
+      <c r="BJ1" s="7" t="inlineStr">
+        <is>
+          <t>solicitud_id</t>
         </is>
       </c>
     </row>
@@ -1117,6 +1123,7 @@
           <t>HS pendiente de validación inicial</t>
         </is>
       </c>
+      <c r="BJ2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
@@ -1324,6 +1331,7 @@
         </is>
       </c>
       <c r="BI3" s="15" t="inlineStr"/>
+      <c r="BJ3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
@@ -1539,6 +1547,7 @@
         </is>
       </c>
       <c r="BI4" s="15" t="inlineStr"/>
+      <c r="BJ4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -1742,6 +1751,7 @@
         </is>
       </c>
       <c r="BI5" s="15" t="inlineStr"/>
+      <c r="BJ5" s="15" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -1969,6 +1979,7 @@
           <t>Candidiasis oral leve secundaria a Bimekizumab</t>
         </is>
       </c>
+      <c r="BJ6" s="15" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -2164,6 +2175,7 @@
           <t>HS sin respuesta a Ixekizumab, pendiente de nueva alternativa</t>
         </is>
       </c>
+      <c r="BJ7" s="15" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -2367,6 +2379,7 @@
           <t>Cambio terapéutico: Taltz → Cosentyx</t>
         </is>
       </c>
+      <c r="BJ8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -2570,6 +2583,7 @@
           <t>Adición de Bimzelx a Cosentyx por respuesta parcial</t>
         </is>
       </c>
+      <c r="BJ9" s="15" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -2781,6 +2795,7 @@
           <t>Cambio de pauta: Cosentyx 300 mg SC cada 4→2 semanas</t>
         </is>
       </c>
+      <c r="BJ10" s="15" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
@@ -2968,9 +2983,10 @@
           <t>Histórico: Adalimumab suspendido por pérdida de respuesta. Actualmente en Cosentyx.</t>
         </is>
       </c>
+      <c r="BJ11" s="15" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BI1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2981,7 +2997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI13"/>
+  <dimension ref="A1:BJ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3045,6 +3061,7 @@
     <col width="18" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="28" customWidth="1" min="61" max="61"/>
+    <col width="20" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3351,6 +3368,11 @@
       <c r="BI1" s="7" t="inlineStr">
         <is>
           <t>observaciones_generales</t>
+        </is>
+      </c>
+      <c r="BJ1" s="7" t="inlineStr">
+        <is>
+          <t>solicitud_id</t>
         </is>
       </c>
     </row>
@@ -3556,6 +3578,7 @@
         </is>
       </c>
       <c r="BI2" s="15" t="inlineStr"/>
+      <c r="BJ2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
@@ -3747,6 +3770,7 @@
           <t>Baricitinib suspendido por intolerancia. Actualmente en Orencia.</t>
         </is>
       </c>
+      <c r="BJ3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
@@ -3950,6 +3974,7 @@
           <t>Cambio terapéutico: Orencia (Abatacept) → Benlysta (Belimumab)</t>
         </is>
       </c>
+      <c r="BJ4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -4141,6 +4166,7 @@
           <t>Histórico: Abatacept suspendido por cambio a Belimumab</t>
         </is>
       </c>
+      <c r="BJ5" s="15" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -4348,6 +4374,7 @@
           <t>Benlysta activo, respuesta parcial</t>
         </is>
       </c>
+      <c r="BJ6" s="15" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -4547,6 +4574,7 @@
         </is>
       </c>
       <c r="BI7" s="15" t="inlineStr"/>
+      <c r="BJ7" s="15" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -4738,6 +4766,7 @@
         </is>
       </c>
       <c r="BI8" s="15" t="inlineStr"/>
+      <c r="BJ8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -4969,6 +4998,7 @@
           <t>EA hepático bajo seguimiento, continuar RoActemra</t>
         </is>
       </c>
+      <c r="BJ9" s="15" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -5176,6 +5206,7 @@
         </is>
       </c>
       <c r="BI10" s="15" t="inlineStr"/>
+      <c r="BJ10" s="15" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
@@ -5391,6 +5422,7 @@
         </is>
       </c>
       <c r="BI11" s="15" t="inlineStr"/>
+      <c r="BJ11" s="15" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -5598,6 +5630,7 @@
           <t>Adherencia baja a Olumiant, valorar intervención educativa</t>
         </is>
       </c>
+      <c r="BJ12" s="15" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
@@ -5793,9 +5826,10 @@
           <t>Varios fármacos activos: Orencia (principal) + RoActemra (concomitante)</t>
         </is>
       </c>
+      <c r="BJ13" s="15" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BI1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5806,7 +5840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI11"/>
+  <dimension ref="A1:BJ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5870,6 +5904,7 @@
     <col width="18" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="28" customWidth="1" min="61" max="61"/>
+    <col width="20" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6176,6 +6211,11 @@
       <c r="BI1" s="7" t="inlineStr">
         <is>
           <t>observaciones_generales</t>
+        </is>
+      </c>
+      <c r="BJ1" s="7" t="inlineStr">
+        <is>
+          <t>solicitud_id</t>
         </is>
       </c>
     </row>
@@ -6381,6 +6421,7 @@
         </is>
       </c>
       <c r="BI2" s="15" t="inlineStr"/>
+      <c r="BJ2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
@@ -6584,6 +6625,7 @@
         </is>
       </c>
       <c r="BI3" s="15" t="inlineStr"/>
+      <c r="BJ3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
@@ -6795,6 +6837,7 @@
         </is>
       </c>
       <c r="BI4" s="15" t="inlineStr"/>
+      <c r="BJ4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -7006,6 +7049,7 @@
           <t>Falta de adherencia a Humira. Valorar intervención educativa.</t>
         </is>
       </c>
+      <c r="BJ5" s="15" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -7205,6 +7249,7 @@
         </is>
       </c>
       <c r="BI6" s="15" t="inlineStr"/>
+      <c r="BJ6" s="15" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -7428,6 +7473,7 @@
           <t>Suspensión por reacción infusional severa a Vedolizumab</t>
         </is>
       </c>
+      <c r="BJ7" s="15" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -7631,6 +7677,7 @@
         </is>
       </c>
       <c r="BI8" s="15" t="inlineStr"/>
+      <c r="BJ8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -7838,6 +7885,7 @@
         </is>
       </c>
       <c r="BI9" s="15" t="inlineStr"/>
+      <c r="BJ9" s="15" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -8041,6 +8089,7 @@
         </is>
       </c>
       <c r="BI10" s="15" t="inlineStr"/>
+      <c r="BJ10" s="15" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
@@ -8248,9 +8297,10 @@
           <t>Renovación de tratamiento. Todo correcto.</t>
         </is>
       </c>
+      <c r="BJ11" s="15" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BI1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8261,7 +8311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI12"/>
+  <dimension ref="A1:BJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8325,6 +8375,7 @@
     <col width="18" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="28" customWidth="1" min="61" max="61"/>
+    <col width="20" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8631,6 +8682,11 @@
       <c r="BI1" s="7" t="inlineStr">
         <is>
           <t>observaciones_generales</t>
+        </is>
+      </c>
+      <c r="BJ1" s="7" t="inlineStr">
+        <is>
+          <t>solicitud_id</t>
         </is>
       </c>
     </row>
@@ -8828,6 +8884,7 @@
           <t>Fármaco extranjero: Pembrolizumab importado vía medicamentos extranjeros</t>
         </is>
       </c>
+      <c r="BJ2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
@@ -9019,6 +9076,7 @@
           <t>Uso compasivo Osimertinib para CPNM EGFR+ sin alternativa</t>
         </is>
       </c>
+      <c r="BJ3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
@@ -9222,6 +9280,7 @@
           <t>Ensayo clínico fase III: Atezolizumab en TNBC</t>
         </is>
       </c>
+      <c r="BJ4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -9429,6 +9488,7 @@
           <t>Uso fuera de ficha técnica: Bevacizumab en 3ª línea CCR</t>
         </is>
       </c>
+      <c r="BJ5" s="15" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -9620,6 +9680,7 @@
           <t>Preparación especial: Rituximab IV con protocolo de premedicación</t>
         </is>
       </c>
+      <c r="BJ6" s="15" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -9819,6 +9880,7 @@
           <t>Pendiente de normalización en catálogo de farmacia</t>
         </is>
       </c>
+      <c r="BJ7" s="15" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -10042,6 +10104,7 @@
           <t>Colitis inmunomediada grado 2 por Nivolumab. Resuelto con corticoides.</t>
         </is>
       </c>
+      <c r="BJ8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -10241,6 +10304,7 @@
           <t>Renovación de tratamiento. Respuesta mantenida.</t>
         </is>
       </c>
+      <c r="BJ9" s="15" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -10440,6 +10504,7 @@
         </is>
       </c>
       <c r="BI10" s="15" t="inlineStr"/>
+      <c r="BJ10" s="15" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
@@ -10631,6 +10696,7 @@
           <t>Suspensión por progresión oncológica</t>
         </is>
       </c>
+      <c r="BJ11" s="15" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -10826,9 +10892,10 @@
           <t>Trastuzumab como concomitante a quimioterapia</t>
         </is>
       </c>
+      <c r="BJ12" s="15" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BI1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10839,7 +10906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G167"/>
+  <dimension ref="A1:G166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -11316,419 +11383,445 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>rechazado</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>no_aplica</t>
+          <t>denegado</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>requiere_prebiologico</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>requiere_prebiologico</t>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
           <t>FALSE</t>
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>tb_estado</t>
+        </is>
+      </c>
+    </row>
     <row r="85">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>tb_estado</t>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Negativo</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Negativo</t>
+          <t>Positivo</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Positivo</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>No realizado</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>No realizado</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
           <t>No aplica</t>
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>serologias_estado</t>
+        </is>
+      </c>
+    </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>serologias_estado</t>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Negativo</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Negativo</t>
+          <t>Positivo</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Positivo</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>No realizado</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>No realizado</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
           <t>No aplica</t>
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>vacunas_estado</t>
+        </is>
+      </c>
+    </row>
     <row r="99">
-      <c r="A99" s="10" t="inlineStr">
-        <is>
-          <t>vacunas_estado</t>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Completo</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Incompleto</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Incompleto</t>
+          <t>Pendiente</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
           <t>No aplica</t>
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>adherencia_morisky</t>
+        </is>
+      </c>
+    </row>
     <row r="105">
-      <c r="A105" s="10" t="inlineStr">
-        <is>
-          <t>adherencia_morisky</t>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Baja</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
           <t>No evaluada</t>
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>hay_efecto_adverso</t>
+        </is>
+      </c>
+    </row>
     <row r="111">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>hay_efecto_adverso</t>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
           <t>FALSE</t>
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>ea_gravedad</t>
+        </is>
+      </c>
+    </row>
     <row r="115">
-      <c r="A115" s="10" t="inlineStr">
-        <is>
-          <t>ea_gravedad</t>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Grave</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Grave</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Moderado</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
           <t>Leve</t>
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>causalidad_naranjo</t>
+        </is>
+      </c>
+    </row>
     <row r="120">
-      <c r="A120" s="10" t="inlineStr">
-        <is>
-          <t>causalidad_naranjo</t>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Definitiva</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Definitiva</t>
+          <t>Probable</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Probable</t>
+          <t>Posible</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Posible</t>
+          <t>Dudosa</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Dudosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
           <t>No evaluada</t>
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>causalidad_karch</t>
+        </is>
+      </c>
+    </row>
     <row r="127">
-      <c r="A127" s="10" t="inlineStr">
-        <is>
-          <t>causalidad_karch</t>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Definitiva</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Definitiva</t>
+          <t>Probable</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Probable</t>
+          <t>Posible</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Posible</t>
+          <t>Dudosa</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Dudosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
           <t>No evaluada</t>
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>demo_flag</t>
+        </is>
+      </c>
+    </row>
     <row r="134">
-      <c r="A134" s="10" t="inlineStr">
-        <is>
-          <t>demo_flag</t>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>CATÁLOGO DE FÁRMACOS ESPECIALES</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>marca_nombre_visible</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>principio_activo</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>categoria_especial</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>indicacion_uso</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>observaciones</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>fecha_alta_catalogo</t>
+        </is>
+      </c>
+      <c r="G140" s="11" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>Fármaco en investigación X</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>Principio activo X</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>ensayo_clinico</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t>Artritis Reumatoide refractaria</t>
+        </is>
+      </c>
+      <c r="E141" s="8" t="inlineStr">
+        <is>
+          <t>Ensayo fase III - hospital</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
           <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="9" t="inlineStr">
-        <is>
-          <t>CATÁLOGO DE FÁRMACOS ESPECIALES</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="11" t="inlineStr">
-        <is>
-          <t>marca_nombre_visible</t>
-        </is>
-      </c>
-      <c r="B141" s="11" t="inlineStr">
-        <is>
-          <t>principio_activo</t>
-        </is>
-      </c>
-      <c r="C141" s="11" t="inlineStr">
-        <is>
-          <t>categoria_especial</t>
-        </is>
-      </c>
-      <c r="D141" s="11" t="inlineStr">
-        <is>
-          <t>indicacion_uso</t>
-        </is>
-      </c>
-      <c r="E141" s="11" t="inlineStr">
-        <is>
-          <t>observaciones</t>
-        </is>
-      </c>
-      <c r="F141" s="11" t="inlineStr">
-        <is>
-          <t>fecha_alta_catalogo</t>
-        </is>
-      </c>
-      <c r="G141" s="11" t="inlineStr">
-        <is>
-          <t>activo</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t>Fármaco en investigación X</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="inlineStr">
-        <is>
-          <t>Principio activo X</t>
-        </is>
-      </c>
+          <t>Medicamento extranjero Y</t>
+        </is>
+      </c>
+      <c r="B142" s="8" t="inlineStr"/>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>ensayo_clinico</t>
+          <t>medicacion_extranjera</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Artritis Reumatoide refractaria</t>
+          <t>LES</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Ensayo fase III - hospital</t>
+          <t>Importado vía medicamentos extranjeros</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G142" s="8" t="inlineStr">
@@ -11737,168 +11830,170 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="8" t="inlineStr">
-        <is>
-          <t>Medicamento extranjero Y</t>
-        </is>
-      </c>
-      <c r="B143" s="8" t="inlineStr"/>
-      <c r="C143" s="8" t="inlineStr">
-        <is>
-          <t>medicacion_extranjera</t>
-        </is>
-      </c>
-      <c r="D143" s="8" t="inlineStr">
-        <is>
-          <t>LES</t>
-        </is>
-      </c>
-      <c r="E143" s="8" t="inlineStr">
-        <is>
-          <t>Importado vía medicamentos extranjeros</t>
-        </is>
-      </c>
-      <c r="F143" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+    <row r="144">
+      <c r="A144" s="12" t="inlineStr">
+        <is>
+          <t>Categorías de fármaco especial:</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="12" t="inlineStr">
-        <is>
-          <t>Categorías de fármaco especial:</t>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>fuera_de_ficha_tecnica</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>fuera_de_ficha_tecnica</t>
+          <t>ensayo_clinico</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ensayo_clinico</t>
+          <t>uso_compasivo</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>uso_compasivo</t>
+          <t>medicacion_extranjera</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>medicacion_extranjera</t>
+          <t>preparacion_especial</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>preparacion_especial</t>
+          <t>pendiente_normalizacion</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>pendiente_normalizacion</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
           <t>otro</t>
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" s="16" t="inlineStr">
+        <is>
+          <t>FÁRMACOS ESPECIALES (sintéticos)</t>
+        </is>
+      </c>
+    </row>
     <row r="154">
-      <c r="A154" s="16" t="inlineStr">
-        <is>
-          <t>FÁRMACOS ESPECIALES (sintéticos)</t>
+      <c r="A154" s="13" t="inlineStr">
+        <is>
+          <t>marca_nombre_visible</t>
+        </is>
+      </c>
+      <c r="B154" s="13" t="inlineStr">
+        <is>
+          <t>principio_activo</t>
+        </is>
+      </c>
+      <c r="C154" s="13" t="inlineStr">
+        <is>
+          <t>categoria_especial</t>
+        </is>
+      </c>
+      <c r="D154" s="13" t="inlineStr">
+        <is>
+          <t>indicacion_uso</t>
+        </is>
+      </c>
+      <c r="E154" s="13" t="inlineStr">
+        <is>
+          <t>observaciones</t>
+        </is>
+      </c>
+      <c r="F154" s="13" t="inlineStr">
+        <is>
+          <t>fecha_alta_catalogo</t>
+        </is>
+      </c>
+      <c r="G154" s="13" t="inlineStr">
+        <is>
+          <t>activo</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="13" t="inlineStr">
-        <is>
-          <t>marca_nombre_visible</t>
-        </is>
-      </c>
-      <c r="B155" s="13" t="inlineStr">
-        <is>
-          <t>principio_activo</t>
-        </is>
-      </c>
-      <c r="C155" s="13" t="inlineStr">
-        <is>
-          <t>categoria_especial</t>
-        </is>
-      </c>
-      <c r="D155" s="13" t="inlineStr">
-        <is>
-          <t>indicacion_uso</t>
-        </is>
-      </c>
-      <c r="E155" s="13" t="inlineStr">
-        <is>
-          <t>observaciones</t>
-        </is>
-      </c>
-      <c r="F155" s="13" t="inlineStr">
-        <is>
-          <t>fecha_alta_catalogo</t>
-        </is>
-      </c>
-      <c r="G155" s="13" t="inlineStr">
-        <is>
-          <t>activo</t>
-        </is>
+      <c r="A155" s="17" t="inlineStr">
+        <is>
+          <t>KEYTRUDA-IMP</t>
+        </is>
+      </c>
+      <c r="B155" s="17" t="inlineStr">
+        <is>
+          <t>Pembrolizumab (importación)</t>
+        </is>
+      </c>
+      <c r="C155" s="17" t="inlineStr">
+        <is>
+          <t>medicacion_extranjera</t>
+        </is>
+      </c>
+      <c r="D155" s="17" t="inlineStr">
+        <is>
+          <t>Melanoma metastásico. Importación desde UE.</t>
+        </is>
+      </c>
+      <c r="E155" s="17" t="inlineStr">
+        <is>
+          <t>Importado del Reino Unido por desabastecimiento local.</t>
+        </is>
+      </c>
+      <c r="F155" s="17" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="G155" s="17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="17" t="inlineStr">
         <is>
-          <t>KEYTRUDA-IMP</t>
+          <t>Compasivo-OSIM-001</t>
         </is>
       </c>
       <c r="B156" s="17" t="inlineStr">
         <is>
-          <t>Pembrolizumab (importación)</t>
+          <t>Osimertinib (uso compasivo)</t>
         </is>
       </c>
       <c r="C156" s="17" t="inlineStr">
         <is>
-          <t>medicacion_extranjera</t>
+          <t>uso_compasivo</t>
         </is>
       </c>
       <c r="D156" s="17" t="inlineStr">
         <is>
-          <t>Melanoma metastásico. Importación desde UE.</t>
+          <t>CPNM EGFR+ sin alternativa terapéutica.</t>
         </is>
       </c>
       <c r="E156" s="17" t="inlineStr">
         <is>
-          <t>Importado del Reino Unido por desabastecimiento local.</t>
+          <t>Aprobado por comité autonómico uso compasivo.</t>
         </is>
       </c>
       <c r="F156" s="17" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G156" s="17" t="b">
@@ -11908,32 +12003,32 @@
     <row r="157">
       <c r="A157" s="17" t="inlineStr">
         <is>
-          <t>Compasivo-OSIM-001</t>
+          <t>EC-TECENTRIQ-001</t>
         </is>
       </c>
       <c r="B157" s="17" t="inlineStr">
         <is>
-          <t>Osimertinib (uso compasivo)</t>
+          <t>Atezolizumab (ensayo clínico)</t>
         </is>
       </c>
       <c r="C157" s="17" t="inlineStr">
         <is>
-          <t>uso_compasivo</t>
+          <t>ensayo_clinico</t>
         </is>
       </c>
       <c r="D157" s="17" t="inlineStr">
         <is>
-          <t>CPNM EGFR+ sin alternativa terapéutica.</t>
+          <t>Cáncer mama triple negativo. Estudio IMpassion-131.</t>
         </is>
       </c>
       <c r="E157" s="17" t="inlineStr">
         <is>
-          <t>Aprobado por comité autonómico uso compasivo.</t>
+          <t>Ensayo fase III promovido por Roche.</t>
         </is>
       </c>
       <c r="F157" s="17" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="G157" s="17" t="b">
@@ -11943,32 +12038,32 @@
     <row r="158">
       <c r="A158" s="17" t="inlineStr">
         <is>
-          <t>EC-TECENTRIQ-001</t>
+          <t>Avastin-off-label</t>
         </is>
       </c>
       <c r="B158" s="17" t="inlineStr">
         <is>
-          <t>Atezolizumab (ensayo clínico)</t>
+          <t>Bevacizumab (3ª línea CCR)</t>
         </is>
       </c>
       <c r="C158" s="17" t="inlineStr">
         <is>
-          <t>ensayo_clinico</t>
+          <t>fuera_de_ficha_tecnica</t>
         </is>
       </c>
       <c r="D158" s="17" t="inlineStr">
         <is>
-          <t>Cáncer mama triple negativo. Estudio IMpassion-131.</t>
+          <t>CCR metastásico KRAS wt, 3ª línea.</t>
         </is>
       </c>
       <c r="E158" s="17" t="inlineStr">
         <is>
-          <t>Ensayo fase III promovido por Roche.</t>
+          <t>Uso off-label aprobado por comité de tumores.</t>
         </is>
       </c>
       <c r="F158" s="17" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G158" s="17" t="b">
@@ -11978,32 +12073,32 @@
     <row r="159">
       <c r="A159" s="17" t="inlineStr">
         <is>
-          <t>Avastin-off-label</t>
+          <t>PREP-ESP-RTX-001</t>
         </is>
       </c>
       <c r="B159" s="17" t="inlineStr">
         <is>
-          <t>Bevacizumab (3ª línea CCR)</t>
+          <t>Rituximab (preparación especial)</t>
         </is>
       </c>
       <c r="C159" s="17" t="inlineStr">
         <is>
-          <t>fuera_de_ficha_tecnica</t>
+          <t>preparacion_especial</t>
         </is>
       </c>
       <c r="D159" s="17" t="inlineStr">
         <is>
-          <t>CCR metastásico KRAS wt, 3ª línea.</t>
+          <t>Linfoma B. Preparación en cabina de citostáticos.</t>
         </is>
       </c>
       <c r="E159" s="17" t="inlineStr">
         <is>
-          <t>Uso off-label aprobado por comité de tumores.</t>
+          <t>Requiere premeditación y bomba de infusión.</t>
         </is>
       </c>
       <c r="F159" s="17" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G159" s="17" t="b">
@@ -12013,32 +12108,32 @@
     <row r="160">
       <c r="A160" s="17" t="inlineStr">
         <is>
-          <t>PREP-ESP-RTX-001</t>
+          <t>PEND-NORM-TRAST-001</t>
         </is>
       </c>
       <c r="B160" s="17" t="inlineStr">
         <is>
-          <t>Rituximab (preparación especial)</t>
+          <t>Trastuzumab (pendiente normalización)</t>
         </is>
       </c>
       <c r="C160" s="17" t="inlineStr">
         <is>
-          <t>preparacion_especial</t>
+          <t>pendiente_normalizacion</t>
         </is>
       </c>
       <c r="D160" s="17" t="inlineStr">
         <is>
-          <t>Linfoma B. Preparación en cabina de citostáticos.</t>
+          <t>Cáncer gástrico HER2+. En proceso de inclusión en catálogo.</t>
         </is>
       </c>
       <c r="E160" s="17" t="inlineStr">
         <is>
-          <t>Requiere premeditación y bomba de infusión.</t>
+          <t>Pendiente de código nacional definitivo.</t>
         </is>
       </c>
       <c r="F160" s="17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G160" s="17" t="b">
@@ -12048,32 +12143,32 @@
     <row r="161">
       <c r="A161" s="17" t="inlineStr">
         <is>
-          <t>PEND-NORM-TRAST-001</t>
+          <t>Bevacizumab-OVARIO</t>
         </is>
       </c>
       <c r="B161" s="17" t="inlineStr">
         <is>
-          <t>Trastuzumab (pendiente normalización)</t>
+          <t>Bevacizumab (cáncer ovario)</t>
         </is>
       </c>
       <c r="C161" s="17" t="inlineStr">
         <is>
-          <t>pendiente_normalizacion</t>
+          <t>fuera_de_ficha_tecnica</t>
         </is>
       </c>
       <c r="D161" s="17" t="inlineStr">
         <is>
-          <t>Cáncer gástrico HER2+. En proceso de inclusión en catálogo.</t>
+          <t>Cáncer de ovario BRCA+ en combinación.</t>
         </is>
       </c>
       <c r="E161" s="17" t="inlineStr">
         <is>
-          <t>Pendiente de código nacional definitivo.</t>
+          <t>Aprobado por comité de tumores para esta indicación.</t>
         </is>
       </c>
       <c r="F161" s="17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G161" s="17" t="b">
@@ -12083,32 +12178,32 @@
     <row r="162">
       <c r="A162" s="17" t="inlineStr">
         <is>
-          <t>Bevacizumab-OVARIO</t>
+          <t>Nivolumab-COLITIS</t>
         </is>
       </c>
       <c r="B162" s="17" t="inlineStr">
         <is>
-          <t>Bevacizumab (cáncer ovario)</t>
+          <t>Nivolumab (colitis inmunomediada)</t>
         </is>
       </c>
       <c r="C162" s="17" t="inlineStr">
         <is>
-          <t>fuera_de_ficha_tecnica</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="D162" s="17" t="inlineStr">
         <is>
-          <t>Cáncer de ovario BRCA+ en combinación.</t>
+          <t>Manejo de EA: colitis por inmunoterapia.</t>
         </is>
       </c>
       <c r="E162" s="17" t="inlineStr">
         <is>
-          <t>Aprobado por comité de tumores para esta indicación.</t>
+          <t>Riesgo de colitis recurrente, monitorización estrecha.</t>
         </is>
       </c>
       <c r="F162" s="17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G162" s="17" t="b">
@@ -12118,32 +12213,32 @@
     <row r="163">
       <c r="A163" s="17" t="inlineStr">
         <is>
-          <t>Nivolumab-COLITIS</t>
+          <t>Rituximab-LINFOMA-PREP</t>
         </is>
       </c>
       <c r="B163" s="17" t="inlineStr">
         <is>
-          <t>Nivolumab (colitis inmunomediada)</t>
+          <t>Rituximab (preparación especial linfoma)</t>
         </is>
       </c>
       <c r="C163" s="17" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>preparacion_especial</t>
         </is>
       </c>
       <c r="D163" s="17" t="inlineStr">
         <is>
-          <t>Manejo de EA: colitis por inmunoterapia.</t>
+          <t>Protocolo R-CHOP modificado.</t>
         </is>
       </c>
       <c r="E163" s="17" t="inlineStr">
         <is>
-          <t>Riesgo de colitis recurrente, monitorización estrecha.</t>
+          <t>Preparación en cabina con cadena fría.</t>
         </is>
       </c>
       <c r="F163" s="17" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G163" s="17" t="b">
@@ -12153,32 +12248,32 @@
     <row r="164">
       <c r="A164" s="17" t="inlineStr">
         <is>
-          <t>Rituximab-LINFOMA-PREP</t>
+          <t>Pembrolizumab-MEL-EXT</t>
         </is>
       </c>
       <c r="B164" s="17" t="inlineStr">
         <is>
-          <t>Rituximab (preparación especial linfoma)</t>
+          <t>Pembrolizumab (importación melanoma)</t>
         </is>
       </c>
       <c r="C164" s="17" t="inlineStr">
         <is>
-          <t>preparacion_especial</t>
+          <t>medicacion_extranjera</t>
         </is>
       </c>
       <c r="D164" s="17" t="inlineStr">
         <is>
-          <t>Protocolo R-CHOP modificado.</t>
+          <t>Melanoma metastásico. Importación temporal.</t>
         </is>
       </c>
       <c r="E164" s="17" t="inlineStr">
         <is>
-          <t>Preparación en cabina con cadena fría.</t>
+          <t>Lote importado de Francia por cupo.</t>
         </is>
       </c>
       <c r="F164" s="17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G164" s="17" t="b">
@@ -12188,32 +12283,32 @@
     <row r="165">
       <c r="A165" s="17" t="inlineStr">
         <is>
-          <t>Pembrolizumab-MEL-EXT</t>
+          <t>Trastuzumab-PEND-CAT</t>
         </is>
       </c>
       <c r="B165" s="17" t="inlineStr">
         <is>
-          <t>Pembrolizumab (importación melanoma)</t>
+          <t>Trastuzumab (pendiente catálogo)</t>
         </is>
       </c>
       <c r="C165" s="17" t="inlineStr">
         <is>
-          <t>medicacion_extranjera</t>
+          <t>pendiente_normalizacion</t>
         </is>
       </c>
       <c r="D165" s="17" t="inlineStr">
         <is>
-          <t>Melanoma metastásico. Importación temporal.</t>
+          <t>Cáncer gástrico HER2+. Nuevo formato.</t>
         </is>
       </c>
       <c r="E165" s="17" t="inlineStr">
         <is>
-          <t>Lote importado de Francia por cupo.</t>
+          <t>Pendiente de asignación de código nacional.</t>
         </is>
       </c>
       <c r="F165" s="17" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G165" s="17" t="b">
@@ -12223,70 +12318,35 @@
     <row r="166">
       <c r="A166" s="17" t="inlineStr">
         <is>
-          <t>Trastuzumab-PEND-CAT</t>
+          <t>Osimertinib-COMP</t>
         </is>
       </c>
       <c r="B166" s="17" t="inlineStr">
         <is>
-          <t>Trastuzumab (pendiente catálogo)</t>
+          <t>Osimertinib (uso compasivo CPNM)</t>
         </is>
       </c>
       <c r="C166" s="17" t="inlineStr">
         <is>
-          <t>pendiente_normalizacion</t>
+          <t>uso_compasivo</t>
         </is>
       </c>
       <c r="D166" s="17" t="inlineStr">
         <is>
-          <t>Cáncer gástrico HER2+. Nuevo formato.</t>
+          <t>Segunda línea CPNM EGFR T790M.</t>
         </is>
       </c>
       <c r="E166" s="17" t="inlineStr">
         <is>
-          <t>Pendiente de asignación de código nacional.</t>
+          <t>Renovación uso compasivo aprobada 2026.</t>
         </is>
       </c>
       <c r="F166" s="17" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="G166" s="17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="17" t="inlineStr">
-        <is>
-          <t>Osimertinib-COMP</t>
-        </is>
-      </c>
-      <c r="B167" s="17" t="inlineStr">
-        <is>
-          <t>Osimertinib (uso compasivo CPNM)</t>
-        </is>
-      </c>
-      <c r="C167" s="17" t="inlineStr">
-        <is>
-          <t>uso_compasivo</t>
-        </is>
-      </c>
-      <c r="D167" s="17" t="inlineStr">
-        <is>
-          <t>Segunda línea CPNM EGFR T790M.</t>
-        </is>
-      </c>
-      <c r="E167" s="17" t="inlineStr">
-        <is>
-          <t>Renovación uso compasivo aprobada 2026.</t>
-        </is>
-      </c>
-      <c r="F167" s="17" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="G167" s="17" t="b">
         <v>1</v>
       </c>
     </row>
